--- a/output/balance_sheet_templates/us_renewable_diesel_bal_sheets.xlsx
+++ b/output/balance_sheet_templates/us_renewable_diesel_bal_sheets.xlsx
@@ -2471,45 +2471,47 @@
       </c>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
+      <c r="D42" s="5" t="n">
+        <v>0.014089838595</v>
+      </c>
       <c r="E42" s="14" t="n">
-        <v>11.21</v>
+        <v>1.847225706781</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>5.63</v>
+        <v>0.9784727732605</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>10.84</v>
+        <v>0.261765802228</v>
       </c>
       <c r="H42" s="14" t="n">
-        <v>11.47</v>
+        <v>0.122786948662</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>21.25</v>
+        <v>1.9559604876</v>
       </c>
       <c r="J42" s="14" t="n">
-        <v>22.81</v>
+        <v>1.91983259538</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>25.41</v>
+        <v>1.882775954115</v>
       </c>
       <c r="L42" s="14" t="n">
-        <v>32.38</v>
+        <v>3.3499752822375</v>
       </c>
       <c r="M42" s="14" t="n">
-        <v>26.54</v>
+        <v>5.20806504267</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>26.59</v>
+        <v>12.31428147915</v>
       </c>
       <c r="O42" s="14" t="n">
-        <v>35.91</v>
+        <v>12.707085679995</v>
       </c>
       <c r="P42" s="14" t="n">
-        <v>19.2</v>
+        <v>1.000745751215</v>
       </c>
       <c r="Q42" s="14" t="n">
-        <v>24.97</v>
+        <v>0.6824736209725</v>
       </c>
       <c r="R42" s="14" t="n">
         <v>23.65</v>
@@ -2531,46 +2533,46 @@
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>5.19</v>
+        <v>0.0561007437585</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>5.59</v>
+        <v>0.254033515869</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>8.359999999999999</v>
+        <v>0.843972961783</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>14.49</v>
+        <v>0.3363070536315</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>10.37</v>
+        <v>0.939209884018</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>14.15</v>
+        <v>1.7969592354875</v>
       </c>
       <c r="J43" s="15" t="n">
-        <v>12.77</v>
+        <v>1.077852484765</v>
       </c>
       <c r="K43" s="15" t="n">
-        <v>17.26</v>
+        <v>2.223405803745</v>
       </c>
       <c r="L43" s="15" t="n">
-        <v>31.12</v>
+        <v>3.4492132101</v>
       </c>
       <c r="M43" s="15" t="n">
-        <v>15.08</v>
+        <v>2.0638394256375</v>
       </c>
       <c r="N43" s="15" t="n">
-        <v>22.93</v>
+        <v>11.5364083778825</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>41.96</v>
+        <v>14.1226578432975</v>
       </c>
       <c r="P43" s="15" t="n">
-        <v>16.78</v>
+        <v>4.18824496811</v>
       </c>
       <c r="Q43" s="15" t="n">
-        <v>22.71</v>
+        <v>0.0647016769875</v>
       </c>
       <c r="R43" s="15" t="n">
         <v>21.21</v>
@@ -2594,46 +2596,46 @@
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="5" t="n"/>
       <c r="D44" s="14" t="n">
-        <v>4.67</v>
+        <v>1.90521304043</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>11.21</v>
+        <v>0.25583744529</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>18.02</v>
+        <v>0.650007485106</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>17.35</v>
+        <v>1.6366794986675</v>
       </c>
       <c r="H44" s="14" t="n">
-        <v>19.15</v>
+        <v>1.3220970711235</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>11.55</v>
+        <v>2.6511518943525</v>
       </c>
       <c r="J44" s="14" t="n">
-        <v>19.28</v>
+        <v>3.4274846454275</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>18.98</v>
+        <v>2.57761935144</v>
       </c>
       <c r="L44" s="14" t="n">
-        <v>37.51</v>
+        <v>4.650962393805</v>
       </c>
       <c r="M44" s="14" t="n">
-        <v>23.31</v>
+        <v>6.99196105951</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>33.01</v>
+        <v>13.37860957188</v>
       </c>
       <c r="O44" s="14" t="n">
-        <v>44.02</v>
+        <v>9.714324059107501</v>
       </c>
       <c r="P44" s="14" t="n">
-        <v>20.5</v>
+        <v>2.865141755875</v>
       </c>
       <c r="Q44" s="14" t="n">
-        <v>28.12</v>
+        <v>0.0942981927825</v>
       </c>
       <c r="R44" s="14" t="n">
         <v>26.45</v>
@@ -2658,43 +2660,43 @@
         <v>1.19</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>3.52</v>
+        <v>1.89914533937975</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>10.37</v>
+        <v>0.2577199018485</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>11.17</v>
+        <v>0.605763612797</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>17.64</v>
+        <v>1.7798808621055</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>16</v>
+        <v>1.137694587638</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>18.73</v>
+        <v>2.080250929155</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>17.09</v>
+        <v>3.5308886397925</v>
       </c>
       <c r="K45" s="15" t="n">
-        <v>27.89</v>
+        <v>4.57896765011</v>
       </c>
       <c r="L45" s="15" t="n">
-        <v>42.55</v>
+        <v>6.106284815015</v>
       </c>
       <c r="M45" s="15" t="n">
-        <v>16.46</v>
+        <v>5.8686965429575</v>
       </c>
       <c r="N45" s="15" t="n">
-        <v>17.64</v>
+        <v>11.325978008415</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>43.05</v>
+        <v>14.6734206157</v>
       </c>
       <c r="P45" s="15" t="n">
-        <v>19.3</v>
+        <v>0.832269657975</v>
       </c>
       <c r="Q45" s="15" t="n">
         <v>24.68</v>
@@ -2723,43 +2725,43 @@
         <v>1.31</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>3.24</v>
+        <v>0.914678620002</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>17.18</v>
+        <v>0.1187733964515</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>22.64</v>
+        <v>1.380622976698</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>11.55</v>
+        <v>1.992631481043</v>
       </c>
       <c r="H46" s="14" t="n">
-        <v>20.08</v>
+        <v>1.588070119363</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>14.28</v>
+        <v>1.8233236087675</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>27.13</v>
+        <v>2.07749212419</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>21.21</v>
+        <v>2.950937646055</v>
       </c>
       <c r="L46" s="14" t="n">
-        <v>36.54</v>
+        <v>4.1577792448325</v>
       </c>
       <c r="M46" s="14" t="n">
-        <v>27.26</v>
+        <v>3.1725539505975</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>48.26</v>
+        <v>11.4492744667</v>
       </c>
       <c r="O46" s="14" t="n">
-        <v>26.39</v>
+        <v>9.7621384313425</v>
       </c>
       <c r="P46" s="14" t="n">
-        <v>20.87</v>
+        <v>0.3912863346</v>
       </c>
       <c r="Q46" s="14" t="n">
         <v>28.29</v>
@@ -2787,43 +2789,43 @@
         <v>1.38</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>12.45</v>
+        <v>2.77915692159875</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0</v>
+        <v>0.2883244217945</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>14.53</v>
+        <v>1.192276845242</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>24.61</v>
+        <v>2.691173384865</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>19.4</v>
+        <v>3.078237624973</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>16.93</v>
+        <v>1.8412386095425</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>25.2</v>
+        <v>1.5451451021825</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>25.83</v>
+        <v>2.6611114816825</v>
       </c>
       <c r="L47" s="15" t="n">
-        <v>45.86</v>
+        <v>5.3932280724875</v>
       </c>
       <c r="M47" s="15" t="n">
-        <v>22.51</v>
+        <v>4.01744941402</v>
       </c>
       <c r="N47" s="15" t="n">
-        <v>28.6</v>
+        <v>14.750118469345</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>24.89</v>
+        <v>9.231670694557501</v>
       </c>
       <c r="P47" s="15" t="n">
-        <v>19.31</v>
+        <v>0.3925253521875</v>
       </c>
       <c r="Q47" s="15" t="n">
         <v>25.07</v>
@@ -2850,43 +2852,43 @@
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="5" t="n"/>
       <c r="D48" s="14" t="n">
-        <v>8.69</v>
+        <v>1.1126261524</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>25.33</v>
+        <v>0.843103760772</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>22.47</v>
+        <v>1.9984324492125</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>17.6</v>
+        <v>3.007425862448</v>
       </c>
       <c r="H48" s="14" t="n">
-        <v>16.63</v>
+        <v>2.9265276198725</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>11.68</v>
+        <v>0.7652754603900001</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>22.93</v>
+        <v>2.5834206666625</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>13.36</v>
+        <v>1.76741507488</v>
       </c>
       <c r="L48" s="14" t="n">
-        <v>23.06</v>
+        <v>4.1678509892775</v>
       </c>
       <c r="M48" s="14" t="n">
-        <v>24.91</v>
+        <v>3.226262586855</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>32.89</v>
+        <v>11.710525934275</v>
       </c>
       <c r="O48" s="14" t="n">
-        <v>21.66</v>
+        <v>9.1763411574975</v>
       </c>
       <c r="P48" s="14" t="n">
-        <v>15.15</v>
+        <v>0.0023778699</v>
       </c>
       <c r="Q48" s="14" t="n">
         <v>20.89</v>
@@ -2911,43 +2913,43 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>20.62</v>
+        <v>2.25785514877125</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>7.48</v>
+        <v>0.9591903379134999</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>23.52</v>
+        <v>1.6565729950175</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>23.31</v>
+        <v>3.3182875289095</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>15.58</v>
+        <v>2.61067707677</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>17.81</v>
+        <v>1.8415481684775</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>18.19</v>
+        <v>1.57259041989</v>
       </c>
       <c r="K49" s="15" t="n">
-        <v>18.27</v>
+        <v>1.4324680879425</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>25.07</v>
+        <v>4.28842245468</v>
       </c>
       <c r="M49" s="15" t="n">
-        <v>17.68</v>
+        <v>5.2883673449775</v>
       </c>
       <c r="N49" s="15" t="n">
-        <v>42.13</v>
+        <v>12.611585772555</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>21.5</v>
+        <v>7.9341590320825</v>
       </c>
       <c r="P49" s="15" t="n">
-        <v>16.3</v>
+        <v>0.008255322319999999</v>
       </c>
       <c r="Q49" s="15" t="n">
         <v>21.79</v>
@@ -2976,43 +2978,43 @@
         <v>1.33</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>14.6</v>
+        <v>2.37680106104</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>11.21</v>
+        <v>0.5804561782915</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>13.1</v>
+        <v>1.723403425275</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>17.26</v>
+        <v>3.58644924477</v>
       </c>
       <c r="H50" s="14" t="n">
-        <v>17.39</v>
+        <v>0.3835337360085</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>13.61</v>
+        <v>2.2522381986825</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>13.65</v>
+        <v>2.3354141652975</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>21.71</v>
+        <v>1.7394266071875</v>
       </c>
       <c r="L50" s="14" t="n">
-        <v>26.71</v>
+        <v>4.25149588304</v>
       </c>
       <c r="M50" s="14" t="n">
-        <v>12.77</v>
+        <v>5.7918433085975</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>17.01</v>
+        <v>12.4953336676875</v>
       </c>
       <c r="O50" s="14" t="n">
-        <v>22.55</v>
+        <v>9.308456824729999</v>
       </c>
       <c r="P50" s="14" t="n">
-        <v>13.17</v>
+        <v>0.0171643391325</v>
       </c>
       <c r="Q50" s="14" t="n">
         <v>16.37</v>
@@ -3040,43 +3042,43 @@
         <v>2.71</v>
       </c>
       <c r="D51" s="15" t="n">
-        <v>11.12</v>
+        <v>3.501593075386</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>9.869999999999999</v>
+        <v>0.9669755897375</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>25.16</v>
+        <v>1.499493812418</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>23.27</v>
+        <v>3.8431873451195</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>16.25</v>
+        <v>0.9398428179385</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>14.32</v>
+        <v>3.587254562745</v>
       </c>
       <c r="J51" s="15" t="n">
-        <v>29.23</v>
+        <v>2.106000687525</v>
       </c>
       <c r="K51" s="15" t="n">
-        <v>25.91</v>
+        <v>3.012079944615</v>
       </c>
       <c r="L51" s="15" t="n">
-        <v>33.39</v>
+        <v>4.5520752979975</v>
       </c>
       <c r="M51" s="15" t="n">
-        <v>18.94</v>
+        <v>5.84718556366</v>
       </c>
       <c r="N51" s="15" t="n">
-        <v>14.74</v>
+        <v>13.28801503134</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>20.68</v>
+        <v>9.9975334571175</v>
       </c>
       <c r="P51" s="15" t="n">
-        <v>14.86</v>
+        <v>4.7027923159875</v>
       </c>
       <c r="Q51" s="15" t="n">
         <v>18.22</v>
@@ -3105,43 +3107,43 @@
         <v>1.36</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>17.33</v>
+        <v>4.198622242304</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>0</v>
+        <v>2.13866461004</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>19.82</v>
+        <v>1.219500509108</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>21.46</v>
+        <v>5.2129241707025</v>
       </c>
       <c r="H52" s="14" t="n">
-        <v>14.49</v>
+        <v>0.942166104649</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>14.45</v>
+        <v>3.6103079337675</v>
       </c>
       <c r="J52" s="14" t="n">
-        <v>20.96</v>
+        <v>2.75104559737</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>27.09</v>
+        <v>4.00311486694</v>
       </c>
       <c r="L52" s="14" t="n">
-        <v>37.38</v>
+        <v>6.92804956998</v>
       </c>
       <c r="M52" s="14" t="n">
-        <v>29.06</v>
+        <v>9.364731140589999</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>34.15</v>
+        <v>11.2163050531875</v>
       </c>
       <c r="O52" s="14" t="n">
-        <v>19.02</v>
+        <v>9.6208335870325</v>
       </c>
       <c r="P52" s="14" t="n">
-        <v>19.18</v>
+        <v>3.5451104232425</v>
       </c>
       <c r="Q52" s="14" t="n">
         <v>24.65</v>
@@ -3169,43 +3171,43 @@
         <v>5.12</v>
       </c>
       <c r="D53" s="15" t="n">
-        <v>15.74</v>
+        <v>3.66863274064</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>11.21</v>
+        <v>0.8397132436455</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>20.29</v>
+        <v>1.9947982444425</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>23.39</v>
+        <v>6.7827910543995</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>12.56</v>
+        <v>3.240551177857</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>4.45</v>
+        <v>4.855950795395</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>28.77</v>
+        <v>3.3785607947175</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>36.71</v>
+        <v>1.9109557780425</v>
       </c>
       <c r="L53" s="15" t="n">
-        <v>20.71</v>
+        <v>5.870634274855</v>
       </c>
       <c r="M53" s="15" t="n">
-        <v>28.14</v>
+        <v>6.592509029855</v>
       </c>
       <c r="N53" s="15" t="n">
-        <v>44.18</v>
+        <v>13.1982009303725</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>-7.65</v>
+        <v>10.2629906547175</v>
       </c>
       <c r="P53" s="15" t="n">
-        <v>15.96</v>
+        <v>2.573479778205</v>
       </c>
       <c r="Q53" s="15" t="n">
         <v>18</v>
@@ -3392,20 +3394,48 @@
       </c>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="5" t="n"/>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="5" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="n"/>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="n"/>
-      <c r="O58" s="5" t="n"/>
-      <c r="P58" s="5" t="n"/>
-      <c r="Q58" s="5" t="n"/>
+      <c r="D58" s="5" t="n">
+        <v>0.03293818017</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0.27057601263</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.0442813162575</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0854906573675</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0.0856512754825</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>0.1699084446325</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0.172283016325</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0.0637039267025</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>0.3346851018875</v>
+      </c>
+      <c r="M58" s="5" t="n">
+        <v>0.4213862570925</v>
+      </c>
+      <c r="N58" s="5" t="n">
+        <v>0.330921327905</v>
+      </c>
+      <c r="O58" s="5" t="n">
+        <v>0.212164634395</v>
+      </c>
+      <c r="P58" s="5" t="n">
+        <v>0.39207204995</v>
+      </c>
+      <c r="Q58" s="5" t="n">
+        <v>0.055106882845</v>
+      </c>
       <c r="R58" s="5" t="n"/>
       <c r="S58" s="5" t="n"/>
       <c r="T58" s="5" t="n"/>
@@ -3417,6 +3447,48 @@
           <t>Feb</t>
         </is>
       </c>
+      <c r="D59" t="n">
+        <v>0.075345508805</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.28353046267</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.04717591662</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.09889387733750001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.1183424234475</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.208166367115</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.184343701045</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.1798223311325</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.2452841211625</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.24958842643</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.30982093443</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.429507966265</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.1122300420325</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.10045898177</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -3426,20 +3498,48 @@
       </c>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="n"/>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
-      <c r="N60" s="5" t="n"/>
-      <c r="O60" s="5" t="n"/>
-      <c r="P60" s="5" t="n"/>
-      <c r="Q60" s="5" t="n"/>
+      <c r="D60" s="5" t="n">
+        <v>0.3549018526725</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0.18426509339</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0.3843052333225</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.470780559515</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>0.275063340195</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>0.5180549430175</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>0.455529416265</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>0.45387144957</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>0.537637270835</v>
+      </c>
+      <c r="M60" s="5" t="n">
+        <v>0.419450704435</v>
+      </c>
+      <c r="N60" s="5" t="n">
+        <v>0.525491373015</v>
+      </c>
+      <c r="O60" s="5" t="n">
+        <v>0.636739877375</v>
+      </c>
+      <c r="P60" s="5" t="n">
+        <v>0.215183751685</v>
+      </c>
+      <c r="Q60" s="5" t="n">
+        <v>0.40446952658</v>
+      </c>
       <c r="R60" s="5" t="n"/>
       <c r="S60" s="5" t="n"/>
       <c r="T60" s="5" t="n"/>
@@ -3451,6 +3551,45 @@
           <t>Apr</t>
         </is>
       </c>
+      <c r="D61" t="n">
+        <v>0.747599661305</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.526159295025</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.483919847635</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.49497813463</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.5711603474325</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.43831416825</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.745677905735</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1.049524829955</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.9955109194975</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.96386979423</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2.300618760195</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.863428855905</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.308059968545</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -3460,19 +3599,45 @@
       </c>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="5" t="n"/>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="5" t="n"/>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
-      <c r="L62" s="5" t="n"/>
-      <c r="M62" s="5" t="n"/>
-      <c r="N62" s="5" t="n"/>
-      <c r="O62" s="5" t="n"/>
-      <c r="P62" s="5" t="n"/>
+      <c r="D62" s="5" t="n">
+        <v>1.134803870025</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0.41830790526</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0.5134916385375</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.6757295173125</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0.48228246934</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>0.7924768401725</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>0.887331873925</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>1.0004484181475</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>1.13640498986</v>
+      </c>
+      <c r="M62" s="5" t="n">
+        <v>1.22003730107</v>
+      </c>
+      <c r="N62" s="5" t="n">
+        <v>1.5292708513075</v>
+      </c>
+      <c r="O62" s="5" t="n">
+        <v>1.0152935981825</v>
+      </c>
+      <c r="P62" s="5" t="n">
+        <v>0.445516877015</v>
+      </c>
       <c r="Q62" s="5" t="n"/>
       <c r="R62" s="5" t="n"/>
       <c r="S62" s="5" t="n"/>
@@ -3485,6 +3650,45 @@
           <t>Jun</t>
         </is>
       </c>
+      <c r="D63" t="n">
+        <v>1.1836751984925</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.5308110581375</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.5236994816375</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.44400846217</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.4554459045675</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.548429652925</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.604715822165</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1.053258993815</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1.3264422556525</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.189704382755</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1.6901742014325</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.966836782835</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.5140461813725</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -3494,19 +3698,45 @@
       </c>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="5" t="n"/>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
-      <c r="K64" s="5" t="n"/>
-      <c r="L64" s="5" t="n"/>
-      <c r="M64" s="5" t="n"/>
-      <c r="N64" s="5" t="n"/>
-      <c r="O64" s="5" t="n"/>
-      <c r="P64" s="5" t="n"/>
+      <c r="D64" s="5" t="n">
+        <v>0.8642319607775</v>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0.6451572874425</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0.5139672019825</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.5180159394375</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>0.91315570388</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0.518369387935</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>0.7895325559975001</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>0.75765437818</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>0.986327192025</v>
+      </c>
+      <c r="M64" s="5" t="n">
+        <v>1.0964403748025</v>
+      </c>
+      <c r="N64" s="5" t="n">
+        <v>1.393471266145</v>
+      </c>
+      <c r="O64" s="5" t="n">
+        <v>1.2643683154375</v>
+      </c>
+      <c r="P64" s="5" t="n">
+        <v>0.61594138991</v>
+      </c>
       <c r="Q64" s="5" t="n"/>
       <c r="R64" s="5" t="n"/>
       <c r="S64" s="5" t="n"/>
@@ -3519,6 +3749,45 @@
           <t>Aug</t>
         </is>
       </c>
+      <c r="D65" t="n">
+        <v>1.383909955995</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.5324388142149999</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.55331279248</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.499557881235</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.7824997873175</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.530885819765</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.58647904637</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1.03208242326</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1.106140013265</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.686804037625</v>
+      </c>
+      <c r="N65" t="n">
+        <v>1.1134857685175</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.17181635158</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.5064818888325</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -3528,19 +3797,45 @@
       </c>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="5" t="n"/>
-      <c r="D66" s="5" t="n"/>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="n"/>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="n"/>
-      <c r="L66" s="5" t="n"/>
-      <c r="M66" s="5" t="n"/>
-      <c r="N66" s="5" t="n"/>
-      <c r="O66" s="5" t="n"/>
-      <c r="P66" s="5" t="n"/>
+      <c r="D66" s="5" t="n">
+        <v>1.029141055775</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0.2746137839025</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.406272069595</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.30265205355</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0.2022503332675</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>0.3846330178075</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>0.47910287691</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>0.85771651854</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>0.7886777084725</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>1.29170443486</v>
+      </c>
+      <c r="N66" s="5" t="n">
+        <v>0.8255697478875</v>
+      </c>
+      <c r="O66" s="5" t="n">
+        <v>0.9727886462175001</v>
+      </c>
+      <c r="P66" s="5" t="n">
+        <v>0.35425321799</v>
+      </c>
       <c r="Q66" s="5" t="n"/>
       <c r="R66" s="5" t="n"/>
       <c r="S66" s="5" t="n"/>
@@ -3553,6 +3848,45 @@
           <t>Oct</t>
         </is>
       </c>
+      <c r="D67" t="n">
+        <v>0.835512072115</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.0796275385675</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.3239161391025</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.2285076062325</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.4386051366725</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.380678457985</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.3184059969825</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.2272356720375</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.43092699314</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.9444989264375</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.9086285577775</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.2735289039</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.1773733409525</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -3562,19 +3896,45 @@
       </c>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="5" t="n"/>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="5" t="n"/>
-      <c r="I68" s="5" t="n"/>
-      <c r="J68" s="5" t="n"/>
-      <c r="K68" s="5" t="n"/>
-      <c r="L68" s="5" t="n"/>
-      <c r="M68" s="5" t="n"/>
-      <c r="N68" s="5" t="n"/>
-      <c r="O68" s="5" t="n"/>
-      <c r="P68" s="5" t="n"/>
+      <c r="D68" s="5" t="n">
+        <v>0.8219154641600001</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0.1311514679125</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.1527547902475</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.2817648786925</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>0.099544999785</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0.2867996861275</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>0.1126887058325</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>0.1467254773075</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>0.168804320195</v>
+      </c>
+      <c r="M68" s="5" t="n">
+        <v>0.44961599886</v>
+      </c>
+      <c r="N68" s="5" t="n">
+        <v>0.72832843279</v>
+      </c>
+      <c r="O68" s="5" t="n">
+        <v>0.5907162677675</v>
+      </c>
+      <c r="P68" s="5" t="n">
+        <v>0.1453653275375</v>
+      </c>
       <c r="Q68" s="5" t="n"/>
       <c r="R68" s="5" t="n"/>
       <c r="S68" s="5" t="n"/>
@@ -3586,6 +3946,45 @@
         <is>
           <t>Dec</t>
         </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.9586491049975</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.1018650408125</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.26899076302</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.2047832783675</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.07093407237</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.1552537930825</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.1659364275625</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.12993756727</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.6170729655475</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.929923954855</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.790069698775</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.2759927205875</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.1397601928275</v>
       </c>
     </row>
     <row r="70">

--- a/output/balance_sheet_templates/us_renewable_diesel_bal_sheets.xlsx
+++ b/output/balance_sheet_templates/us_renewable_diesel_bal_sheets.xlsx
@@ -2472,46 +2472,46 @@
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="5" t="n"/>
       <c r="D42" s="5" t="n">
-        <v>0.014089838595</v>
+        <v>0.04696612865</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>1.847225706781</v>
+        <v>0.825968409595</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>0.9784727732605</v>
+        <v>1.0866974051325</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>0.261765802228</v>
+        <v>0.66850725032</v>
       </c>
       <c r="H42" s="14" t="n">
-        <v>0.122786948662</v>
+        <v>0.37094627164</v>
       </c>
       <c r="I42" s="14" t="n">
-        <v>1.9559604876</v>
+        <v>0.920852705815</v>
       </c>
       <c r="J42" s="14" t="n">
-        <v>1.91983259538</v>
+        <v>1.304121613445</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>1.882775954115</v>
+        <v>1.03530043533</v>
       </c>
       <c r="L42" s="14" t="n">
-        <v>3.3499752822375</v>
+        <v>0.82569913349</v>
       </c>
       <c r="M42" s="14" t="n">
-        <v>5.20806504267</v>
+        <v>1.73300499568</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>12.31428147915</v>
+        <v>3.40352051312</v>
       </c>
       <c r="O42" s="14" t="n">
-        <v>12.707085679995</v>
+        <v>4.1584220152825</v>
       </c>
       <c r="P42" s="14" t="n">
-        <v>1.000745751215</v>
+        <v>0.1871449823775</v>
       </c>
       <c r="Q42" s="14" t="n">
-        <v>0.6824736209725</v>
+        <v>0.09333830604</v>
       </c>
       <c r="R42" s="14" t="n">
         <v>23.65</v>
@@ -2533,46 +2533,46 @@
         </is>
       </c>
       <c r="D43" s="15" t="n">
-        <v>0.0561007437585</v>
+        <v>0.187002479195</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>0.254033515869</v>
+        <v>0.4880463762825</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>0.843972961783</v>
+        <v>1.04507899223</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>0.3363070536315</v>
+        <v>0.5255133828875</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>0.939209884018</v>
+        <v>1.25962730131</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>1.7969592354875</v>
+        <v>0.9428168729700001</v>
       </c>
       <c r="J43" s="15" t="n">
-        <v>1.077852484765</v>
+        <v>0.90253602054</v>
       </c>
       <c r="K43" s="15" t="n">
-        <v>2.223405803745</v>
+        <v>1.368940449415</v>
       </c>
       <c r="L43" s="15" t="n">
-        <v>3.4492132101</v>
+        <v>0.91156514162</v>
       </c>
       <c r="M43" s="15" t="n">
-        <v>2.0638394256375</v>
+        <v>0.462223719475</v>
       </c>
       <c r="N43" s="15" t="n">
-        <v>11.5364083778825</v>
+        <v>3.15661543547</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>14.1226578432975</v>
+        <v>4.6817509350675</v>
       </c>
       <c r="P43" s="15" t="n">
-        <v>4.18824496811</v>
+        <v>0.56387464469</v>
       </c>
       <c r="Q43" s="15" t="n">
-        <v>0.0647016769875</v>
+        <v>0.013139578585</v>
       </c>
       <c r="R43" s="15" t="n">
         <v>21.21</v>
@@ -2596,46 +2596,46 @@
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="5" t="n"/>
       <c r="D44" s="14" t="n">
-        <v>1.90521304043</v>
+        <v>1.166586718885</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>0.25583744529</v>
+        <v>0.8527029903</v>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0.650007485106</v>
+        <v>0.916450785495</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>1.6366794986675</v>
+        <v>1.6509172697325</v>
       </c>
       <c r="H44" s="14" t="n">
-        <v>1.3220970711235</v>
+        <v>1.576794386055</v>
       </c>
       <c r="I44" s="14" t="n">
-        <v>2.6511518943525</v>
+        <v>1.245686343335</v>
       </c>
       <c r="J44" s="14" t="n">
-        <v>3.4274846454275</v>
+        <v>2.4563007107275</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>2.57761935144</v>
+        <v>1.2135972646</v>
       </c>
       <c r="L44" s="14" t="n">
-        <v>4.650962393805</v>
+        <v>1.22062013038</v>
       </c>
       <c r="M44" s="14" t="n">
-        <v>6.99196105951</v>
+        <v>2.693797171765</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>13.37860957188</v>
+        <v>3.5878745708225</v>
       </c>
       <c r="O44" s="14" t="n">
-        <v>9.714324059107501</v>
+        <v>3.14014329174</v>
       </c>
       <c r="P44" s="14" t="n">
-        <v>2.865141755875</v>
+        <v>0.383822333755</v>
       </c>
       <c r="Q44" s="14" t="n">
-        <v>0.0942981927825</v>
+        <v>0.015768994185</v>
       </c>
       <c r="R44" s="14" t="n">
         <v>26.45</v>
@@ -2660,43 +2660,43 @@
         <v>1.19</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>1.89914533937975</v>
+        <v>1.08116123178</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>0.2577199018485</v>
+        <v>0.56250382447</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>0.605763612797</v>
+        <v>0.764231967135</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>1.7798808621055</v>
+        <v>2.38021972874</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>1.137694587638</v>
+        <v>1.5178681164675</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>2.080250929155</v>
+        <v>1.41926043294</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>3.5308886397925</v>
+        <v>1.58080561289</v>
       </c>
       <c r="K45" s="15" t="n">
-        <v>4.57896765011</v>
+        <v>2.146985473605</v>
       </c>
       <c r="L45" s="15" t="n">
-        <v>6.106284815015</v>
+        <v>1.765703175005</v>
       </c>
       <c r="M45" s="15" t="n">
-        <v>5.8686965429575</v>
+        <v>1.88471895878</v>
       </c>
       <c r="N45" s="15" t="n">
-        <v>11.325978008415</v>
+        <v>3.43693073353</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>14.6734206157</v>
+        <v>5.562886799995</v>
       </c>
       <c r="P45" s="15" t="n">
-        <v>0.832269657975</v>
+        <v>0.11298358274</v>
       </c>
       <c r="Q45" s="15" t="n">
         <v>24.68</v>
@@ -2725,43 +2725,43 @@
         <v>1.31</v>
       </c>
       <c r="D46" s="14" t="n">
-        <v>0.914678620002</v>
+        <v>1.070190027095</v>
       </c>
       <c r="E46" s="14" t="n">
-        <v>0.1187733964515</v>
+        <v>0.395736320105</v>
       </c>
       <c r="F46" s="14" t="n">
-        <v>1.380622976698</v>
+        <v>1.112542352495</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>1.992631481043</v>
+        <v>2.4992160867275</v>
       </c>
       <c r="H46" s="14" t="n">
-        <v>1.588070119363</v>
+        <v>2.03719887357</v>
       </c>
       <c r="I46" s="14" t="n">
-        <v>1.8233236087675</v>
+        <v>1.34051783663</v>
       </c>
       <c r="J46" s="14" t="n">
-        <v>2.07749212419</v>
+        <v>1.091172592615</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>2.950937646055</v>
+        <v>1.67652072931</v>
       </c>
       <c r="L46" s="14" t="n">
-        <v>4.1577792448325</v>
+        <v>1.10207277334</v>
       </c>
       <c r="M46" s="14" t="n">
-        <v>3.1725539505975</v>
+        <v>1.115473225615</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>11.4492744667</v>
+        <v>3.04279880814</v>
       </c>
       <c r="O46" s="14" t="n">
-        <v>9.7621384313425</v>
+        <v>3.5373647676675</v>
       </c>
       <c r="P46" s="14" t="n">
-        <v>0.3912863346</v>
+        <v>0.05533996671</v>
       </c>
       <c r="Q46" s="14" t="n">
         <v>28.29</v>
@@ -2789,43 +2789,43 @@
         <v>1.38</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>2.77915692159875</v>
+        <v>1.766586218705</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.2883244217945</v>
+        <v>0.5125644230875001</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>1.192276845242</v>
+        <v>1.50632134786</v>
       </c>
       <c r="G47" s="15" t="n">
-        <v>2.691173384865</v>
+        <v>3.28784398873</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>3.078237624973</v>
+        <v>3.3790209665275</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>1.8412386095425</v>
+        <v>1.22919832035</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>1.5451451021825</v>
+        <v>0.97153286895</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>2.6611114816825</v>
+        <v>1.54927262112</v>
       </c>
       <c r="L47" s="15" t="n">
-        <v>5.3932280724875</v>
+        <v>1.614847067925</v>
       </c>
       <c r="M47" s="15" t="n">
-        <v>4.01744941402</v>
+        <v>1.283682939875</v>
       </c>
       <c r="N47" s="15" t="n">
-        <v>14.750118469345</v>
+        <v>3.557798422815</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>9.231670694557501</v>
+        <v>2.481577741825</v>
       </c>
       <c r="P47" s="15" t="n">
-        <v>0.3925253521875</v>
+        <v>0.05339499501</v>
       </c>
       <c r="Q47" s="15" t="n">
         <v>25.07</v>
@@ -2852,43 +2852,43 @@
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="5" t="n"/>
       <c r="D48" s="14" t="n">
-        <v>1.1126261524</v>
+        <v>0.8538706686300001</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>0.843103760772</v>
+        <v>1.2385760784425</v>
       </c>
       <c r="F48" s="14" t="n">
-        <v>1.9984324492125</v>
+        <v>2.7826209586525</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>3.007425862448</v>
+        <v>3.5392789786725</v>
       </c>
       <c r="H48" s="14" t="n">
-        <v>2.9265276198725</v>
+        <v>3.35016296251</v>
       </c>
       <c r="I48" s="14" t="n">
-        <v>0.7652754603900001</v>
+        <v>0.512118927285</v>
       </c>
       <c r="J48" s="14" t="n">
-        <v>2.5834206666625</v>
+        <v>1.36334490005</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>1.76741507488</v>
+        <v>1.269992553865</v>
       </c>
       <c r="L48" s="14" t="n">
-        <v>4.1678509892775</v>
+        <v>1.12958044696</v>
       </c>
       <c r="M48" s="14" t="n">
-        <v>3.226262586855</v>
+        <v>0.842478148225</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>11.710525934275</v>
+        <v>2.677679563895</v>
       </c>
       <c r="O48" s="14" t="n">
-        <v>9.1763411574975</v>
+        <v>2.1659393390075</v>
       </c>
       <c r="P48" s="14" t="n">
-        <v>0.0023778699</v>
+        <v>0.0031751888</v>
       </c>
       <c r="Q48" s="14" t="n">
         <v>20.89</v>
@@ -2913,43 +2913,43 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>2.25785514877125</v>
+        <v>1.622420914205</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>0.9591903379134999</v>
+        <v>1.499364513955</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>1.6565729950175</v>
+        <v>1.96038734878</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>3.3182875289095</v>
+        <v>3.9894864350075</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>2.61067707677</v>
+        <v>3.2890204329325</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>1.8415481684775</v>
+        <v>1.227753738575</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>1.57259041989</v>
+        <v>0.81916376731</v>
       </c>
       <c r="K49" s="15" t="n">
-        <v>1.4324680879425</v>
+        <v>0.9570634550575</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>4.28842245468</v>
+        <v>0.958767252765</v>
       </c>
       <c r="M49" s="15" t="n">
-        <v>5.2883673449775</v>
+        <v>1.42864838816</v>
       </c>
       <c r="N49" s="15" t="n">
-        <v>12.611585772555</v>
+        <v>3.3818768319525</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>7.9341590320825</v>
+        <v>2.05872679992</v>
       </c>
       <c r="P49" s="15" t="n">
-        <v>0.008255322319999999</v>
+        <v>0.00308913892</v>
       </c>
       <c r="Q49" s="15" t="n">
         <v>21.79</v>
@@ -2978,43 +2978,43 @@
         <v>1.33</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>2.37680106104</v>
+        <v>1.69821839558</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>0.5804561782915</v>
+        <v>0.83546483167</v>
       </c>
       <c r="F50" s="14" t="n">
-        <v>1.723403425275</v>
+        <v>1.8772196137625</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>3.58644924477</v>
+        <v>3.8094524760425</v>
       </c>
       <c r="H50" s="14" t="n">
-        <v>0.3835337360085</v>
+        <v>0.820869984305</v>
       </c>
       <c r="I50" s="14" t="n">
-        <v>2.2522381986825</v>
+        <v>0.98584915135</v>
       </c>
       <c r="J50" s="14" t="n">
-        <v>2.3354141652975</v>
+        <v>1.062892531925</v>
       </c>
       <c r="K50" s="14" t="n">
-        <v>1.7394266071875</v>
+        <v>1.320380625095</v>
       </c>
       <c r="L50" s="14" t="n">
-        <v>4.25149588304</v>
+        <v>1.48560448708</v>
       </c>
       <c r="M50" s="14" t="n">
-        <v>5.7918433085975</v>
+        <v>1.668724117445</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>12.4953336676875</v>
+        <v>4.6018589281175</v>
       </c>
       <c r="O50" s="14" t="n">
-        <v>9.308456824729999</v>
+        <v>2.25036376558</v>
       </c>
       <c r="P50" s="14" t="n">
-        <v>0.0171643391325</v>
+        <v>0.004620664545</v>
       </c>
       <c r="Q50" s="14" t="n">
         <v>16.37</v>
@@ -3042,43 +3042,43 @@
         <v>2.71</v>
       </c>
       <c r="D51" s="15" t="n">
-        <v>3.501593075386</v>
+        <v>2.64350421804</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>0.9669755897375</v>
+        <v>1.49968862925</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>1.499493812418</v>
+        <v>1.91819088419</v>
       </c>
       <c r="G51" s="15" t="n">
-        <v>3.8431873451195</v>
+        <v>3.7543865562875</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>0.9398428179385</v>
+        <v>1.27907920056</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>3.587254562745</v>
+        <v>1.8944427999</v>
       </c>
       <c r="J51" s="15" t="n">
-        <v>2.106000687525</v>
+        <v>1.17639620504</v>
       </c>
       <c r="K51" s="15" t="n">
-        <v>3.012079944615</v>
+        <v>1.604667910125</v>
       </c>
       <c r="L51" s="15" t="n">
-        <v>4.5520752979975</v>
+        <v>1.513805720385</v>
       </c>
       <c r="M51" s="15" t="n">
-        <v>5.84718556366</v>
+        <v>1.597745355605</v>
       </c>
       <c r="N51" s="15" t="n">
-        <v>13.28801503134</v>
+        <v>4.232185783385</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>9.9975334571175</v>
+        <v>1.797153388765</v>
       </c>
       <c r="P51" s="15" t="n">
-        <v>4.7027923159875</v>
+        <v>0.630820125425</v>
       </c>
       <c r="Q51" s="15" t="n">
         <v>18.22</v>
@@ -3107,43 +3107,43 @@
         <v>1.36</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>4.198622242304</v>
+        <v>3.3255107351725</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>2.13866461004</v>
+        <v>2.2650985907375</v>
       </c>
       <c r="F52" s="14" t="n">
-        <v>1.219500509108</v>
+        <v>1.5663668874525</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>5.2129241707025</v>
+        <v>4.6186885319225</v>
       </c>
       <c r="H52" s="14" t="n">
-        <v>0.942166104649</v>
+        <v>0.817203993935</v>
       </c>
       <c r="I52" s="14" t="n">
-        <v>3.6103079337675</v>
+        <v>1.70858328844</v>
       </c>
       <c r="J52" s="14" t="n">
-        <v>2.75104559737</v>
+        <v>1.351355719385</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>4.00311486694</v>
+        <v>2.050708173465</v>
       </c>
       <c r="L52" s="14" t="n">
-        <v>6.92804956998</v>
+        <v>2.37243769882</v>
       </c>
       <c r="M52" s="14" t="n">
-        <v>9.364731140589999</v>
+        <v>3.0372104474075</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>11.2163050531875</v>
+        <v>4.067349866755</v>
       </c>
       <c r="O52" s="14" t="n">
-        <v>9.6208335870325</v>
+        <v>1.96041680163</v>
       </c>
       <c r="P52" s="14" t="n">
-        <v>3.5451104232425</v>
+        <v>0.4763315067</v>
       </c>
       <c r="Q52" s="14" t="n">
         <v>24.65</v>
@@ -3171,43 +3171,43 @@
         <v>5.12</v>
       </c>
       <c r="D53" s="15" t="n">
-        <v>3.66863274064</v>
+        <v>4.4766934028075</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>0.8397132436455</v>
+        <v>1.32029635864</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1.9947982444425</v>
+        <v>2.17675890516</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>6.7827910543995</v>
+        <v>5.943072775325</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>3.240551177857</v>
+        <v>1.83748793809</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>4.855950795395</v>
+        <v>2.322421806565</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>3.3785607947175</v>
+        <v>1.93210715264</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>1.9109557780425</v>
+        <v>1.047997661305</v>
       </c>
       <c r="L53" s="15" t="n">
-        <v>5.870634274855</v>
+        <v>2.34955799953</v>
       </c>
       <c r="M53" s="15" t="n">
-        <v>6.592509029855</v>
+        <v>2.29884714794</v>
       </c>
       <c r="N53" s="15" t="n">
-        <v>13.1982009303725</v>
+        <v>4.044560982175</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>10.2629906547175</v>
+        <v>2.49258122876</v>
       </c>
       <c r="P53" s="15" t="n">
-        <v>2.573479778205</v>
+        <v>0.34368147492</v>
       </c>
       <c r="Q53" s="15" t="n">
         <v>18</v>

--- a/output/balance_sheet_templates/us_renewable_diesel_bal_sheets.xlsx
+++ b/output/balance_sheet_templates/us_renewable_diesel_bal_sheets.xlsx
@@ -2508,10 +2508,10 @@
         <v>4.1584220152825</v>
       </c>
       <c r="P42" s="14" t="n">
-        <v>0.1871449823775</v>
+        <v>0.1872678223575</v>
       </c>
       <c r="Q42" s="14" t="n">
-        <v>0.09333830604</v>
+        <v>0.093338570212</v>
       </c>
       <c r="R42" s="14" t="n">
         <v>23.65</v>
@@ -2569,7 +2569,7 @@
         <v>4.6817509350675</v>
       </c>
       <c r="P43" s="15" t="n">
-        <v>0.56387464469</v>
+        <v>0.563887589118</v>
       </c>
       <c r="Q43" s="15" t="n">
         <v>0.013139578585</v>
@@ -2632,7 +2632,7 @@
         <v>3.14014329174</v>
       </c>
       <c r="P44" s="14" t="n">
-        <v>0.383822333755</v>
+        <v>0.385143193755</v>
       </c>
       <c r="Q44" s="14" t="n">
         <v>0.015768994185</v>
@@ -2696,7 +2696,7 @@
         <v>5.562886799995</v>
       </c>
       <c r="P45" s="15" t="n">
-        <v>0.11298358274</v>
+        <v>0.112988602008</v>
       </c>
       <c r="Q45" s="15" t="n">
         <v>24.68</v>
@@ -2749,19 +2749,19 @@
         <v>1.67652072931</v>
       </c>
       <c r="L46" s="14" t="n">
-        <v>1.10207277334</v>
+        <v>1.143188239248</v>
       </c>
       <c r="M46" s="14" t="n">
-        <v>1.115473225615</v>
+        <v>1.141940354123</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>3.04279880814</v>
+        <v>3.08859302434</v>
       </c>
       <c r="O46" s="14" t="n">
-        <v>3.5373647676675</v>
+        <v>3.5989799807755</v>
       </c>
       <c r="P46" s="14" t="n">
-        <v>0.05533996671</v>
+        <v>0.114293118574</v>
       </c>
       <c r="Q46" s="14" t="n">
         <v>28.29</v>
@@ -2792,7 +2792,7 @@
         <v>1.766586218705</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>0.5125644230875001</v>
+        <v>0.5126238617875</v>
       </c>
       <c r="F47" s="15" t="n">
         <v>1.50632134786</v>
@@ -2885,10 +2885,10 @@
         <v>2.677679563895</v>
       </c>
       <c r="O48" s="14" t="n">
-        <v>2.1659393390075</v>
+        <v>2.1685649445155</v>
       </c>
       <c r="P48" s="14" t="n">
-        <v>0.0031751888</v>
+        <v>0.004238745272</v>
       </c>
       <c r="Q48" s="14" t="n">
         <v>20.89</v>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="D49" s="15" t="n">
-        <v>1.622420914205</v>
+        <v>1.622480352905</v>
       </c>
       <c r="E49" s="15" t="n">
         <v>1.499364513955</v>
@@ -2946,10 +2946,10 @@
         <v>3.3818768319525</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>2.05872679992</v>
+        <v>2.059949387936</v>
       </c>
       <c r="P49" s="15" t="n">
-        <v>0.00308913892</v>
+        <v>0.004137637588</v>
       </c>
       <c r="Q49" s="15" t="n">
         <v>21.79</v>
@@ -3008,13 +3008,13 @@
         <v>1.668724117445</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>4.6018589281175</v>
+        <v>4.6018628906975</v>
       </c>
       <c r="O50" s="14" t="n">
         <v>2.25036376558</v>
       </c>
       <c r="P50" s="14" t="n">
-        <v>0.004620664545</v>
+        <v>0.006021304489</v>
       </c>
       <c r="Q50" s="14" t="n">
         <v>16.37</v>
@@ -3072,13 +3072,13 @@
         <v>1.597745355605</v>
       </c>
       <c r="N51" s="15" t="n">
-        <v>4.232185783385</v>
+        <v>4.232195293577</v>
       </c>
       <c r="O51" s="15" t="n">
         <v>1.797153388765</v>
       </c>
       <c r="P51" s="15" t="n">
-        <v>0.630820125425</v>
+        <v>0.632213632725</v>
       </c>
       <c r="Q51" s="15" t="n">
         <v>18.22</v>
@@ -3119,7 +3119,7 @@
         <v>4.6186885319225</v>
       </c>
       <c r="H52" s="14" t="n">
-        <v>0.817203993935</v>
+        <v>0.817204258107</v>
       </c>
       <c r="I52" s="14" t="n">
         <v>1.70858328844</v>
@@ -3128,19 +3128,19 @@
         <v>1.351355719385</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>2.050708173465</v>
+        <v>2.050708437637</v>
       </c>
       <c r="L52" s="14" t="n">
         <v>2.37243769882</v>
       </c>
       <c r="M52" s="14" t="n">
-        <v>3.0372104474075</v>
+        <v>3.0372342228875</v>
       </c>
       <c r="N52" s="14" t="n">
         <v>4.067349866755</v>
       </c>
       <c r="O52" s="14" t="n">
-        <v>1.96041680163</v>
+        <v>1.960507676798</v>
       </c>
       <c r="P52" s="14" t="n">
         <v>0.4763315067</v>
@@ -3204,10 +3204,10 @@
         <v>4.044560982175</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>2.49258122876</v>
+        <v>2.49263010058</v>
       </c>
       <c r="P53" s="15" t="n">
-        <v>0.34368147492</v>
+        <v>0.344984371224</v>
       </c>
       <c r="Q53" s="15" t="n">
         <v>18</v>
